--- a/education_forms/008_soil_science_quiz--education_forms.xlsx
+++ b/education_forms/008_soil_science_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what is soil</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is the introduction to the soil science quiz.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>multiple_choice</t>
+          <t>soil_types</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,7 +555,11 @@
           <t>soil types</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose the correct type of soil.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,22 +569,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>soil_composition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>soil composition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>please select in 24 hours format</t>
+          <t>Describe the primary component of soil that affects its structure.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -588,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>soil_processes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>soil processes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose the process by which soil loses its nutrients.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>soil_properties</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>soil properties</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Choose the relationship between pH and soil fertility.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -634,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>conservation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>conservation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Choose the primary goal of soil conservation.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>fertility</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>fertility</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Choose the factor that affects soil fertility.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -685,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>microbiology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>microbiology</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Describe the role of microorganisms in soil formation.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -703,20 +731,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>erosion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>erosion</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Choose the causes of soil erosion.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -731,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select multiple</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Choose the importance of water in soil formation.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -749,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>nutrients</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>select one</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>nutrients</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Choose the essential nutrients for plant growth.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -772,297 +812,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>conclusion</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Summarize what you have learned from this quiz.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>select multiple</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>select one</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1079,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1107,255 +875,493 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>multiple_choice_choices</t>
+          <t>soil_types_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>sand</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>sand</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>multiple_choice_choices</t>
+          <t>soil_types_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>silt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>silt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>multiple_choice_choices</t>
+          <t>soil_types_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>clay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>clay</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>soil_processes_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>leaching</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>leaching</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>soil_processes_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>erosion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>erosion</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>soil_processes_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>weathering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>weathering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>soil_properties_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>ph_affects_soil_fertility</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>pH affects soil fertility</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>soil_properties_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>ph_does_not_affect_soil_fertility</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>pH does not affect soil fertility</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>soil_properties_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>ph_affects_soil_structure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>pH affects soil structure</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>soil_properties_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>ph_does_not_affect_soil_structure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>pH does not affect soil structure</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>conservation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>prevent_soil_erosion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>prevent soil erosion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>conservation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>prevent_soil_erosion_and_improve_fertility</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>prevent soil erosion and improve fertility</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>conservation_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>improve_soil_fertility</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>improve soil fertility</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>fertility_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>organic_matter</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>organic matter</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>fertility_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>pH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fertility_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>water_content</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>water content</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fertility_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>erosion_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>water_erosion</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>water erosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>erosion_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wind_erosion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wind erosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>erosion_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>tillage</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>tillage</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>erosion_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>deforestation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deforestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>water_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>water_affects_soil_formation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>water affects soil formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>water_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>water_does_not_affect_soil_formation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>water does not affect soil formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>water_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>water_affects_soil_fertility</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>water affects soil fertility</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>water_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>water_does_not_affect_soil_fertility</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>water does not affect soil fertility</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>nutrients_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nitrogen</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>nutrients_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>phosphorus</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>phosphorus</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>nutrients_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>potassium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>nutrients_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>magnesium</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>magnesium</t>
         </is>
       </c>
     </row>
